--- a/Colunmnas - atributos .xlsx
+++ b/Colunmnas - atributos .xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos analista de datos\Power BI\Salud Ocupacional\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos analista de datos\Power BI\Salud Ocupacional\Power-bi-imagenes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8E31E5-219E-4EB2-8F97-4B45B382FAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBC70BE-AE8C-483D-BDA3-B0D66AD7AB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DICCIONARIO" sheetId="1" r:id="rId1"/>
@@ -2031,6 +2031,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="12" max="12" width="20.85546875" customWidth="1"/>
+    <col min="13" max="13" width="18.85546875" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3266,6 +3271,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" customWidth="1"/>
     <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
@@ -4232,6 +4243,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.85546875" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
     <col min="15" max="15" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
